--- a/data/trans_bre/P1404-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1404-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>-2,1%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,79</t>
+          <t>-3,15; 4,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,79</t>
+          <t>-7,5; 1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 2,72</t>
+          <t>-6,26; 2,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,06</t>
+          <t>-4,21; 3,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 92,57</t>
+          <t>-41,92; 89,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,29; 12,77</t>
+          <t>-65,9; 17,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 36,68</t>
+          <t>-50,93; 33,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 36,5</t>
+          <t>-26,9; 26,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,89</t>
+          <t>-5,2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-30,6%</t>
+          <t>-32,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1,55</t>
+          <t>-5,44; 2,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 3,02</t>
+          <t>-5,56; 2,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 2,76</t>
+          <t>-6,58; 2,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -1,17</t>
+          <t>-9,52; -1,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,07; 26,81</t>
+          <t>-53,27; 47,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 45,96</t>
+          <t>-52,28; 39,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 34,15</t>
+          <t>-50,54; 30,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,28; -8,02</t>
+          <t>-50,74; -10,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,53</t>
+          <t>-5,87; 4,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -0,12</t>
+          <t>-9,33; -0,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 6,23</t>
+          <t>-6,51; 7,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 19,09</t>
+          <t>-3,56; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 49,38</t>
+          <t>-48,74; 56,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,33; -0,45</t>
+          <t>-60,84; -0,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 52,41</t>
+          <t>-41,84; 64,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 384,55</t>
+          <t>-18,58; 55,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,44</t>
+          <t>-2,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>-18,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,08</t>
+          <t>-3,95; 0,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -0,88</t>
+          <t>-7,03; -0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -0,39</t>
+          <t>-5,99; -0,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 48,63</t>
+          <t>-5,33; -0,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 13,27</t>
+          <t>-38,47; 10,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,56; -8,37</t>
+          <t>-46,92; -6,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,26; -2,07</t>
+          <t>-43,09; -2,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 339,37</t>
+          <t>-31,76; -1,11</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,09</t>
+          <t>-0,76; 7,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,11</t>
+          <t>0,41; 8,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 6,86</t>
+          <t>-0,54; 7,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 8,68</t>
+          <t>3,3; 11,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 128,03</t>
+          <t>-8,06; 122,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 88,12</t>
+          <t>2,5; 86,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 58,12</t>
+          <t>-3,97; 61,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 59,42</t>
+          <t>19,64; 90,09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,92</t>
+          <t>15,57</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>749,35%</t>
+          <t>716,32%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,11</t>
+          <t>10,59; 14,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 20,94</t>
+          <t>14,8; 20,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,65; 18,28</t>
+          <t>12,75; 18,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,37</t>
+          <t>12,69; 18,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>445,76; 4711,75</t>
+          <t>422,84; 4589,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>321,12; 5444,36</t>
+          <t>345,02; 5516,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>374,23; 4018,46</t>
+          <t>336,29; 3822,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>253,27; 2126,88</t>
+          <t>280,98; 2065,81</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,8</t>
+          <t>1,07; 3,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,26</t>
+          <t>0,61; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,52</t>
+          <t>0,32; 3,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 25,6</t>
+          <t>0,2; 3,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,57; 51,99</t>
+          <t>12,97; 51,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,91; 39,69</t>
+          <t>5,07; 38,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 33,2</t>
+          <t>2,45; 33,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,24; 205,76</t>
+          <t>1,32; 24,38</t>
         </is>
       </c>
     </row>
